--- a/artfynd/A 35137-2025 artfynd.xlsx
+++ b/artfynd/A 35137-2025 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>97735988</v>
+        <v>97735879</v>
       </c>
       <c r="B2" t="n">
-        <v>101120</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>107609</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,16 +686,16 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>222002</v>
+        <v>219686</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Underviol</t>
+          <t>Vätteros</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Viola mirabilis</t>
+          <t>Lathraea squamaria</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>570914.4958115395</v>
+        <v>570914</v>
       </c>
       <c r="R2" t="n">
-        <v>6529146.338227036</v>
+        <v>6529146</v>
       </c>
       <c r="S2" t="n">
         <v>50</v>
@@ -745,22 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>1979-09-01</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>1979-05-10</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>1979-09-01</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>1979-05-10</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -792,50 +777,45 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>97736514</v>
+        <v>97736558</v>
       </c>
       <c r="B3" t="n">
-        <v>98520</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106813</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>222498</v>
+        <v>220785</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Kvarntorp, 700 m SSO om, Srm</t>
+          <t>Kvarntorp, 750 m SSO om, Srm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>570914.4958115395</v>
+        <v>571007</v>
       </c>
       <c r="R3" t="n">
-        <v>6529146.338227036</v>
+        <v>6529105</v>
       </c>
       <c r="S3" t="n">
         <v>50</v>
@@ -862,22 +842,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>1979-05-10</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>1979-09-01</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>1979-05-10</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>1979-09-01</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -891,7 +861,7 @@
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>örtrik granskog</t>
+          <t>örtrik sumpskog</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -909,32 +879,27 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>97736022</v>
+        <v>97736559</v>
       </c>
       <c r="B4" t="n">
-        <v>98431</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106813</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>222771</v>
+        <v>220785</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -949,10 +914,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>570914.4958115395</v>
+        <v>570914</v>
       </c>
       <c r="R4" t="n">
-        <v>6529146.338227036</v>
+        <v>6529146</v>
       </c>
       <c r="S4" t="n">
         <v>50</v>
@@ -982,19 +947,9 @@
           <t>1979-09-01</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>1979-09-01</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1026,50 +981,45 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>97736558</v>
+        <v>97735922</v>
       </c>
       <c r="B5" t="n">
-        <v>103813</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>102225</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220785</v>
+        <v>221223</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Vippärt</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Lathyrus niger</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Kvarntorp, 750 m SSO om, Srm</t>
+          <t>Kvarntorp, 700 m SSO om, Srm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>571006.9007616694</v>
+        <v>570914</v>
       </c>
       <c r="R5" t="n">
-        <v>6529105.140609013</v>
+        <v>6529146</v>
       </c>
       <c r="S5" t="n">
         <v>50</v>
@@ -1099,21 +1049,11 @@
           <t>1979-09-01</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>1979-09-01</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
@@ -1125,7 +1065,7 @@
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>örtrik sumpskog</t>
+          <t>örtrik granskog</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1143,32 +1083,27 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>97736559</v>
+        <v>97735988</v>
       </c>
       <c r="B6" t="n">
-        <v>103813</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>103683</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220785</v>
+        <v>222002</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Underviol</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Viola mirabilis</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1183,10 +1118,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>570914.4958115395</v>
+        <v>570914</v>
       </c>
       <c r="R6" t="n">
-        <v>6529146.338227036</v>
+        <v>6529146</v>
       </c>
       <c r="S6" t="n">
         <v>50</v>
@@ -1216,19 +1151,9 @@
           <t>1979-09-01</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>1979-09-01</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1263,12 +1188,7 @@
         <v>97735999</v>
       </c>
       <c r="B7" t="n">
-        <v>101680</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>104628</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1300,10 +1220,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>570914.4958115395</v>
+        <v>570914</v>
       </c>
       <c r="R7" t="n">
-        <v>6529146.338227036</v>
+        <v>6529146</v>
       </c>
       <c r="S7" t="n">
         <v>50</v>
@@ -1333,19 +1253,9 @@
           <t>1979-09-01</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>1979-09-01</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1377,37 +1287,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>97735922</v>
+        <v>97736514</v>
       </c>
       <c r="B8" t="n">
-        <v>99382</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101326</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221223</v>
+        <v>222498</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vippärt</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lathyrus niger</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1417,10 +1322,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>570914.4958115395</v>
+        <v>570914</v>
       </c>
       <c r="R8" t="n">
-        <v>6529146.338227036</v>
+        <v>6529146</v>
       </c>
       <c r="S8" t="n">
         <v>50</v>
@@ -1447,22 +1352,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>1979-09-01</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>1979-05-10</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>1979-09-01</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>1979-05-10</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1494,15 +1389,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>97735879</v>
+        <v>97736022</v>
       </c>
       <c r="B9" t="n">
-        <v>104490</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101228</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1510,16 +1400,16 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>219686</v>
+        <v>222771</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vätteros</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lathraea squamaria</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1534,10 +1424,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>570914.4958115395</v>
+        <v>570914</v>
       </c>
       <c r="R9" t="n">
-        <v>6529146.338227036</v>
+        <v>6529146</v>
       </c>
       <c r="S9" t="n">
         <v>50</v>
@@ -1564,22 +1454,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>1979-05-10</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>1979-09-01</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>1979-05-10</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>1979-09-01</t>
         </is>
       </c>
       <c r="AD9" t="b">

--- a/artfynd/A 35137-2025 artfynd.xlsx
+++ b/artfynd/A 35137-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AZ9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -774,6 +779,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97735879</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -876,6 +886,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97736558</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -978,6 +993,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97736559</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1080,6 +1100,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97735922</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1182,6 +1207,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97735988</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1284,6 +1314,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97735999</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1386,6 +1421,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97736514</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1488,8 +1528,23 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97736022</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>